--- a/isms-core-framework/A.6-people-controls/isms-a.6.4-5-employment-exit/WKBK/90_workbooks/ISMS-IMP-A.6.4-5.S2_Employment_Exit_Assessment_20260208.xlsx
+++ b/isms-core-framework/A.6-people-controls/isms-a.6.4-5-employment-exit/WKBK/90_workbooks/ISMS-IMP-A.6.4-5.S2_Employment_Exit_Assessment_20260208.xlsx
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Active Directory, Azure AD, LDAP</t>
+          <t>Active Directory, Microsoft Entra ID (formerly Azure AD), LDAP</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
